--- a/sampleprojects/StateTax/excel/StateTax.xlsx
+++ b/sampleprojects/StateTax/excel/StateTax.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="284">
   <si>
     <t>DT: Compute Tax</t>
   </si>
@@ -64,6 +64,9 @@
     <t>Y</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -226,19 +229,19 @@
     <t>Single filer</t>
   </si>
   <si>
-    <t>taxpayer.filing_status == SINGLE</t>
+    <t>taxpayer.filing_status == "SINGLE"</t>
   </si>
   <si>
     <t>Married Filing Jointly</t>
   </si>
   <si>
-    <t>taxpayer.filing_status == MFJ</t>
+    <t>taxpayer.filing_status == "MFJ"</t>
   </si>
   <si>
     <t>Head of Household</t>
   </si>
   <si>
-    <t>taxpayer.filing_status == HOH</t>
+    <t>taxpayer.filing_status == "HOH"</t>
   </si>
   <si>
     <t>Default to Single</t>
@@ -1327,7 +1330,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1373,7 +1376,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1396,7 +1399,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1529,67 +1532,67 @@
         <v>1</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D13" s="4">
         <v>1</v>
@@ -1645,58 +1648,58 @@
         <v>1</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -1704,58 +1707,58 @@
         <v>2</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -1763,58 +1766,58 @@
         <v>3</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -1822,58 +1825,58 @@
         <v>4</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -1881,58 +1884,58 @@
         <v>5</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -1940,58 +1943,58 @@
         <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
@@ -1999,58 +2002,58 @@
         <v>7</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
@@ -2058,58 +2061,58 @@
         <v>8</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
@@ -2117,58 +2120,58 @@
         <v>9</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -2176,58 +2179,58 @@
         <v>10</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
@@ -2235,58 +2238,58 @@
         <v>11</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
@@ -2294,58 +2297,58 @@
         <v>12</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26">
@@ -2353,58 +2356,58 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -2443,56 +2446,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -2508,92 +2511,92 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
@@ -2609,174 +2612,174 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
@@ -2792,92 +2795,92 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -2893,133 +2896,133 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -3035,461 +3038,461 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M27" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M28" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M29" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
@@ -3505,461 +3508,461 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M31" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L32" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M32" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M33" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J34" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K34" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L34" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M34" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F35" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L35" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M35" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F36" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H36" s="16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J36" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L36" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M36" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F37" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H37" s="16" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K37" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L37" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M37" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F38" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J38" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L38" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M38" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F39" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H39" s="16" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K39" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L39" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M39" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H40" s="16" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J40" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L40" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M40" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F41" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H41" s="16" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K41" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L41" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M41" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
@@ -3975,576 +3978,576 @@
     </row>
     <row r="43">
       <c r="A43" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H43" s="16" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K43" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M43" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F44" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H44" s="16" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L44" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M44" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H45" s="16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K45" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M45" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H46" s="16" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L46" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M46" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H47" s="16" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K47" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L47" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M47" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H48" s="16" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K48" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L48" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M48" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F49" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H49" s="16" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K49" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M49" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H50" s="16" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K50" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L50" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M50" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F51" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H51" s="16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K51" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L51" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M51" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H52" s="16" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J52" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K52" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L52" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M52" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F53" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H53" s="16" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I53" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K53" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L53" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M53" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H54" s="16" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J54" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K54" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L54" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M54" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H55" s="16" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K55" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L55" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M55" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F56" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H56" s="16" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J56" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K56" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L56" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M56" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -4782,40 +4785,40 @@
         <v>13</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -4823,10 +4826,10 @@
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>13</v>
@@ -4841,40 +4844,40 @@
         <v>13</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -4882,10 +4885,10 @@
         <v>3</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>13</v>
@@ -4900,40 +4903,40 @@
         <v>13</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -4941,10 +4944,10 @@
         <v>4</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>13</v>
@@ -4959,49 +4962,49 @@
         <v>12</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D16" s="4">
         <v>1</v>
@@ -5057,58 +5060,58 @@
         <v>1</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -5116,58 +5119,58 @@
         <v>2</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="F18" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -5175,58 +5178,58 @@
         <v>3</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
@@ -5234,58 +5237,58 @@
         <v>4</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
@@ -5293,58 +5296,58 @@
         <v>5</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
@@ -5352,58 +5355,58 @@
         <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -5411,58 +5414,58 @@
         <v>7</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
@@ -5470,67 +5473,67 @@
         <v>8</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D26" s="1">
         <v>1</v>
@@ -5586,58 +5589,58 @@
         <v>1</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
@@ -5645,58 +5648,58 @@
         <v>2</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
@@ -5704,58 +5707,58 @@
         <v>3</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
@@ -5763,58 +5766,58 @@
         <v>4</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -5845,7 +5848,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5891,7 +5894,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -5914,7 +5917,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -5965,10 +5968,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -6074,67 +6077,67 @@
         <v>1</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D14" s="4">
         <v>1</v>
@@ -6190,67 +6193,67 @@
         <v>1</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -6306,58 +6309,58 @@
         <v>1</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -6389,7 +6392,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6435,7 +6438,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -6458,7 +6461,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -6509,10 +6512,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -6618,67 +6621,67 @@
         <v>1</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D14" s="4">
         <v>1</v>
@@ -6734,67 +6737,67 @@
         <v>1</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -6850,58 +6853,58 @@
         <v>1</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -6933,7 +6936,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6979,7 +6982,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -7002,7 +7005,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -7135,10 +7138,10 @@
         <v>1</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>12</v>
@@ -7153,40 +7156,40 @@
         <v>13</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -7194,10 +7197,10 @@
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>13</v>
@@ -7212,40 +7215,40 @@
         <v>13</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -7253,10 +7256,10 @@
         <v>3</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>13</v>
@@ -7271,40 +7274,40 @@
         <v>13</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -7312,10 +7315,10 @@
         <v>4</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>13</v>
@@ -7330,49 +7333,49 @@
         <v>12</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D16" s="4">
         <v>1</v>
@@ -7428,58 +7431,58 @@
         <v>1</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -7487,58 +7490,58 @@
         <v>2</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -7546,58 +7549,58 @@
         <v>3</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
@@ -7605,58 +7608,58 @@
         <v>4</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
@@ -7664,67 +7667,67 @@
         <v>5</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
@@ -7780,58 +7783,58 @@
         <v>1</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
@@ -7839,58 +7842,58 @@
         <v>2</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26">
@@ -7898,58 +7901,58 @@
         <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
@@ -7957,58 +7960,58 @@
         <v>4</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -8039,7 +8042,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8085,7 +8088,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -8108,7 +8111,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -8241,67 +8244,67 @@
         <v>1</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D13" s="4">
         <v>1</v>
@@ -8357,58 +8360,58 @@
         <v>1</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -8416,67 +8419,67 @@
         <v>2</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -8532,58 +8535,58 @@
         <v>1</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -8591,58 +8594,58 @@
         <v>2</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -8673,7 +8676,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8719,7 +8722,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -8742,7 +8745,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -8875,67 +8878,67 @@
         <v>1</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D13" s="4">
         <v>1</v>
@@ -8991,58 +8994,58 @@
         <v>1</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -9072,7 +9075,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -9118,7 +9121,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -9141,7 +9144,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -9274,10 +9277,10 @@
         <v>1</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>12</v>
@@ -9292,40 +9295,40 @@
         <v>13</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -9333,10 +9336,10 @@
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>13</v>
@@ -9351,40 +9354,40 @@
         <v>13</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -9392,10 +9395,10 @@
         <v>3</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>13</v>
@@ -9410,40 +9413,40 @@
         <v>13</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -9451,10 +9454,10 @@
         <v>4</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>13</v>
@@ -9469,49 +9472,49 @@
         <v>12</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D16" s="4">
         <v>1</v>
@@ -9567,58 +9570,58 @@
         <v>1</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -9626,58 +9629,58 @@
         <v>2</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -9685,58 +9688,58 @@
         <v>3</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
@@ -9744,58 +9747,58 @@
         <v>4</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -9825,7 +9828,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -9871,7 +9874,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -9894,7 +9897,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -9945,10 +9948,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -10054,58 +10057,58 @@
         <v>1</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -10113,67 +10116,67 @@
         <v>2</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D15" s="4">
         <v>1</v>
@@ -10229,58 +10232,58 @@
         <v>1</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -10288,67 +10291,67 @@
         <v>2</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D19" s="1">
         <v>1</v>
@@ -10404,58 +10407,58 @@
         <v>1</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
